--- a/data/trans_camb/IP19C03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 4,7</t>
+          <t>-15,91; 5,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 3,44</t>
+          <t>-17,12; 5,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 2,83</t>
+          <t>-17,78; 3,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 7,85</t>
+          <t>-15,27; 8,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 18,08</t>
+          <t>-5,89; 18,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 2,78</t>
+          <t>-17,03; 2,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 3,19</t>
+          <t>-12,82; 3,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 8,25</t>
+          <t>-9,3; 6,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -0,41</t>
+          <t>-14,19; 0,03</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,88; 52,9</t>
+          <t>-76,33; 56,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,58; 48,94</t>
+          <t>-83,12; 65,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,96; 32,73</t>
+          <t>-76,0; 37,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 102,72</t>
+          <t>-74,89; 106,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 192,4</t>
+          <t>-33,48; 213,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,62; 38,92</t>
+          <t>-76,0; 39,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,51; 31,88</t>
+          <t>-63,84; 35,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 73,75</t>
+          <t>-48,48; 58,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,76; -2,27</t>
+          <t>-67,88; 5,91</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 23,76</t>
+          <t>-2,93; 22,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 20,24</t>
+          <t>-4,79; 19,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 11,98</t>
+          <t>-9,82; 12,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 7,97</t>
+          <t>-19,02; 6,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 6,71</t>
+          <t>-19,59; 6,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 7,23</t>
+          <t>-19,43; 7,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 11,62</t>
+          <t>-6,27; 12,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 8,87</t>
+          <t>-7,14; 10,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 7,59</t>
+          <t>-9,67; 7,25</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 384,87</t>
+          <t>-26,08; 373,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 342,38</t>
+          <t>-32,74; 350,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,13; 198,93</t>
+          <t>-53,12; 229,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,31; 67,97</t>
+          <t>-67,21; 55,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 69,18</t>
+          <t>-72,23; 53,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 64,84</t>
+          <t>-65,53; 74,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 107,14</t>
+          <t>-31,19; 116,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 78,98</t>
+          <t>-35,97; 102,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 79,58</t>
+          <t>-47,66; 71,8</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 17,96</t>
+          <t>-12,61; 17,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 0,19</t>
+          <t>-29,74; -1,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 19,84</t>
+          <t>-13,88; 20,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 21,35</t>
+          <t>-6,87; 21,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,86; 7,28</t>
+          <t>-16,72; 7,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 5,06</t>
+          <t>-18,23; 4,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 13,73</t>
+          <t>-5,15; 14,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,04; -0,7</t>
+          <t>-18,75; -0,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 7,86</t>
+          <t>-12,63; 8,0</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,65; 150,45</t>
+          <t>-46,83; 152,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-92,46; 23,55</t>
+          <t>-100,0; 13,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 157,41</t>
+          <t>-53,34; 161,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 192,93</t>
+          <t>-31,41; 185,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,46; 76,67</t>
+          <t>-76,14; 70,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 64,93</t>
+          <t>-81,58; 50,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 94,92</t>
+          <t>-22,0; 122,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,29; 1,0</t>
+          <t>-80,06; 3,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,15; 61,62</t>
+          <t>-57,13; 56,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 15,26</t>
+          <t>-3,56; 14,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 6,85</t>
+          <t>-10,36; 6,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 11,03</t>
+          <t>-6,57; 12,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 11,63</t>
+          <t>-6,61; 11,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 9,23</t>
+          <t>-8,33; 10,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 18,07</t>
+          <t>-1,48; 18,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 10,3</t>
+          <t>-2,78; 10,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 5,64</t>
+          <t>-7,22; 5,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 12,47</t>
+          <t>-0,81; 12,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 110,31</t>
+          <t>-17,02; 102,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 49,24</t>
+          <t>-42,66; 48,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 76,1</t>
+          <t>-27,26; 83,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 83,39</t>
+          <t>-29,82; 89,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 66,03</t>
+          <t>-37,6; 77,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 131,5</t>
+          <t>-6,38; 141,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 68,76</t>
+          <t>-12,9; 67,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,43; 38,08</t>
+          <t>-32,42; 32,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 80,23</t>
+          <t>-3,7; 84,34</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 6,31</t>
+          <t>-18,17; 4,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 8,37</t>
+          <t>-16,37; 10,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 10,6</t>
+          <t>-20,48; 10,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 16,98</t>
+          <t>-6,13; 17,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 12,16</t>
+          <t>-8,87; 12,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 5,67</t>
+          <t>-16,56; 5,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 9,19</t>
+          <t>-7,47; 8,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 7,61</t>
+          <t>-9,53; 7,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 3,04</t>
+          <t>-14,73; 3,42</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,06; 29,27</t>
+          <t>-49,47; 23,64</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,44; 38,77</t>
+          <t>-44,25; 51,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,5; 48,36</t>
+          <t>-54,14; 47,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 114,65</t>
+          <t>-24,87; 113,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 82,38</t>
+          <t>-36,32; 92,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,71; 36,13</t>
+          <t>-63,52; 39,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 43,23</t>
+          <t>-26,29; 41,85</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 37,05</t>
+          <t>-33,15; 36,73</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,34; 17,99</t>
+          <t>-52,85; 17,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 5,6</t>
+          <t>-25,97; 7,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 13,43</t>
+          <t>-19,38; 13,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 2,48</t>
+          <t>-25,74; 1,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 21,93</t>
+          <t>-1,0; 22,59</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,16; 29,24</t>
+          <t>2,98; 31,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 14,52</t>
+          <t>-9,2; 13,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 11,24</t>
+          <t>-11,32; 9,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 17,19</t>
+          <t>-4,94; 17,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 4,57</t>
+          <t>-15,28; 2,84</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-79,47; 38,64</t>
+          <t>-78,59; 44,49</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-58,64; 78,65</t>
+          <t>-57,01; 81,99</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,6; 16,74</t>
+          <t>-72,83; 15,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 904,48</t>
+          <t>-29,88; 847,49</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1031,79</t>
+          <t>3,39; 1262,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,5; 429,87</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 94,94</t>
+          <t>-49,59; 73,16</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 143,81</t>
+          <t>-24,59; 132,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 48,08</t>
+          <t>-64,62; 24,81</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,95</t>
+          <t>-4,97; 5,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 2,22</t>
+          <t>-7,24; 2,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 2,37</t>
+          <t>-7,65; 2,54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 8,04</t>
+          <t>-1,64; 7,9</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 6,37</t>
+          <t>-3,31; 5,94</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 3,96</t>
+          <t>-5,6; 3,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 5,36</t>
+          <t>-1,38; 5,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 2,89</t>
+          <t>-4,21; 2,79</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 1,23</t>
+          <t>-5,32; 1,47</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 32,53</t>
+          <t>-21,21; 32,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 13,86</t>
+          <t>-32,26; 11,99</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-33,96; 12,91</t>
+          <t>-33,27; 14,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 53,09</t>
+          <t>-8,4; 53,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 42,38</t>
+          <t>-17,12; 40,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-28,64; 26,11</t>
+          <t>-29,13; 23,05</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 31,72</t>
+          <t>-7,22; 32,93</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 16,13</t>
+          <t>-20,44; 16,65</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 7,18</t>
+          <t>-26,26; 8,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 5,36</t>
+          <t>-17,84; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 5,54</t>
+          <t>-18,66; 3,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 3,05</t>
+          <t>-18,14; 1,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 8,96</t>
+          <t>-15,52; 7,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 18,22</t>
+          <t>-6,99; 18,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 2,95</t>
+          <t>-16,93; 3,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 3,14</t>
+          <t>-13,19; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 6,83</t>
+          <t>-9,05; 7,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 0,03</t>
+          <t>-13,29; -0,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,33; 56,85</t>
+          <t>-81,27; 43,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,12; 65,0</t>
+          <t>-83,0; 51,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 37,76</t>
+          <t>-76,91; 18,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,89; 106,35</t>
+          <t>-74,39; 86,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 213,71</t>
+          <t>-34,67; 200,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 39,76</t>
+          <t>-76,95; 40,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,84; 35,98</t>
+          <t>-66,22; 25,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 58,04</t>
+          <t>-47,27; 61,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,88; 5,91</t>
+          <t>-68,43; 3,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 22,94</t>
+          <t>-3,44; 22,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 19,2</t>
+          <t>-5,47; 18,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 12,33</t>
+          <t>-10,61; 12,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 6,82</t>
+          <t>-17,59; 7,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 6,01</t>
+          <t>-19,67; 6,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 7,73</t>
+          <t>-18,72; 6,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 12,56</t>
+          <t>-6,66; 11,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 10,07</t>
+          <t>-8,22; 9,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 7,25</t>
+          <t>-9,53; 7,1</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 373,44</t>
+          <t>-26,39; 372,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,74; 350,43</t>
+          <t>-31,81; 349,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,12; 229,35</t>
+          <t>-58,84; 197,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,21; 55,4</t>
+          <t>-65,29; 77,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,23; 53,58</t>
+          <t>-70,85; 60,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,53; 74,39</t>
+          <t>-65,29; 61,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 116,75</t>
+          <t>-34,55; 108,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 102,02</t>
+          <t>-38,39; 90,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 71,8</t>
+          <t>-46,56; 72,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 17,95</t>
+          <t>-14,48; 17,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,74; -1,8</t>
+          <t>-28,51; -2,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 20,78</t>
+          <t>-13,54; 22,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 21,17</t>
+          <t>-4,71; 21,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 7,99</t>
+          <t>-16,41; 7,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 4,89</t>
+          <t>-18,19; 4,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 14,82</t>
+          <t>-5,29; 14,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,75; -0,03</t>
+          <t>-17,98; 0,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 8,0</t>
+          <t>-13,36; 7,06</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 152,78</t>
+          <t>-49,73; 143,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,46</t>
+          <t>-93,05; 8,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,34; 161,96</t>
+          <t>-52,07; 180,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,41; 185,69</t>
+          <t>-26,53; 193,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,14; 70,96</t>
+          <t>-76,76; 69,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,58; 50,26</t>
+          <t>-80,28; 43,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 122,88</t>
+          <t>-21,8; 106,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,06; 3,92</t>
+          <t>-76,56; 9,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 56,41</t>
+          <t>-57,51; 54,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 14,62</t>
+          <t>-4,12; 16,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 6,77</t>
+          <t>-11,01; 6,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 12,16</t>
+          <t>-6,95; 11,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 11,51</t>
+          <t>-6,1; 11,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 10,06</t>
+          <t>-8,4; 9,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 18,49</t>
+          <t>-1,33; 18,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 10,47</t>
+          <t>-2,7; 11,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 5,03</t>
+          <t>-6,5; 6,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 12,79</t>
+          <t>-0,93; 12,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 102,33</t>
+          <t>-18,91; 109,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 48,98</t>
+          <t>-45,72; 43,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 83,57</t>
+          <t>-29,87; 78,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 89,03</t>
+          <t>-27,89; 81,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 77,26</t>
+          <t>-38,56; 67,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 141,69</t>
+          <t>-7,49; 140,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 67,9</t>
+          <t>-12,94; 75,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 32,84</t>
+          <t>-29,98; 38,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 84,34</t>
+          <t>-3,9; 87,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 4,99</t>
+          <t>-17,94; 5,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 10,89</t>
+          <t>-17,42; 8,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 10,02</t>
+          <t>-18,75; 9,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 17,06</t>
+          <t>-4,81; 17,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 12,96</t>
+          <t>-9,74; 11,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 5,18</t>
+          <t>-15,88; 4,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 8,55</t>
+          <t>-7,84; 9,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 7,12</t>
+          <t>-10,09; 6,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 3,42</t>
+          <t>-15,34; 3,53</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 23,64</t>
+          <t>-49,97; 24,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 51,33</t>
+          <t>-46,37; 39,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 47,19</t>
+          <t>-53,68; 41,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 113,7</t>
+          <t>-18,25; 121,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,32; 92,47</t>
+          <t>-37,13; 70,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 39,93</t>
+          <t>-61,52; 35,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 41,85</t>
+          <t>-27,42; 46,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 36,73</t>
+          <t>-34,95; 34,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,85; 17,17</t>
+          <t>-52,68; 20,35</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 7,5</t>
+          <t>-27,07; 4,32</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 13,2</t>
+          <t>-19,02; 13,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 1,96</t>
+          <t>-26,05; 1,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 22,59</t>
+          <t>0,2; 23,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,98; 31,4</t>
+          <t>1,88; 30,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 13,91</t>
+          <t>-8,93; 14,18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 9,13</t>
+          <t>-9,84; 9,01</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 17,75</t>
+          <t>-5,41; 16,2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 2,84</t>
+          <t>-14,93; 3,41</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-78,59; 44,49</t>
+          <t>-81,37; 31,5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 81,99</t>
+          <t>-56,48; 70,04</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-72,83; 15,24</t>
+          <t>-75,63; 13,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 847,49</t>
+          <t>-26,85; 831,82</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,39; 1262,49</t>
+          <t>-0,65; 1207,09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-88,5; 429,87</t>
+          <t>-85,57; 531,15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-49,59; 73,16</t>
+          <t>-46,99; 72,32</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 132,44</t>
+          <t>-25,77; 124,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-64,62; 24,81</t>
+          <t>-64,81; 30,97</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 5,72</t>
+          <t>-4,61; 5,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 2,17</t>
+          <t>-7,6; 1,96</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 2,54</t>
+          <t>-7,92; 2,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 7,9</t>
+          <t>-1,36; 8,24</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,94</t>
+          <t>-3,63; 6,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 3,6</t>
+          <t>-5,6; 3,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,5</t>
+          <t>-1,97; 5,25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 2,79</t>
+          <t>-4,15; 2,82</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,47</t>
+          <t>-5,11; 1,33</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 32,98</t>
+          <t>-20,25; 32,52</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 11,99</t>
+          <t>-32,59; 11,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 14,81</t>
+          <t>-33,9; 11,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 53,42</t>
+          <t>-7,43; 56,23</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 40,08</t>
+          <t>-19,49; 42,77</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 23,05</t>
+          <t>-28,96; 24,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 32,93</t>
+          <t>-9,41; 31,16</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-20,44; 16,65</t>
+          <t>-19,94; 16,72</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 8,76</t>
+          <t>-25,66; 8,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C03-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,65</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,43</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-6,03</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-7,45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,54</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,65</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,29</t>
+          <t>-6,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,67</t>
+          <t>-6,69</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 4,39</t>
+          <t>-15,05; 7,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 3,24</t>
+          <t>-6,45; 18,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 1,82</t>
+          <t>-17,07; 2,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 7,39</t>
+          <t>-16,86; 4,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 18,61</t>
+          <t>-17,6; 3,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 3,15</t>
+          <t>-16,35; 3,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 3,01</t>
+          <t>-13,17; 3,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 7,05</t>
+          <t>-9,05; 8,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -0,09</t>
+          <t>-14,17; -0,3</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-23,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37,34%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-42,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-37,85%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-46,74%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-43,92%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-23,37%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,34%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-41,57%</t>
+          <t>-43,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-42,89%</t>
+          <t>-43,02%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 43,7</t>
+          <t>-72,63; 102,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,0; 51,31</t>
+          <t>-32,82; 192,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,91; 18,84</t>
+          <t>-77,02; 38,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,39; 86,61</t>
+          <t>-76,88; 52,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 200,37</t>
+          <t>-82,58; 48,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,95; 40,74</t>
+          <t>-75,85; 36,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,22; 25,88</t>
+          <t>-66,51; 31,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 61,92</t>
+          <t>-46,23; 73,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 3,61</t>
+          <t>-68,81; -1,15</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-4,91</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-6,67</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,35</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>10,34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,65</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,67</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,86</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-1,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 22,6</t>
+          <t>-19,08; 7,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 18,86</t>
+          <t>-19,65; 6,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 12,41</t>
+          <t>-18,1; 6,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 7,71</t>
+          <t>-1,74; 23,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 6,78</t>
+          <t>-4,28; 20,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 6,73</t>
+          <t>-10,74; 11,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 11,86</t>
+          <t>-6,39; 11,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 9,22</t>
+          <t>-8,29; 8,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 7,1</t>
+          <t>-9,31; 7,22</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-24,48%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-33,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-26,66%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>89,24%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>66,01%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,67%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-24,48%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-33,28%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-24,25%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-8,16%</t>
+          <t>-10,83%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 372,43</t>
+          <t>-65,31; 67,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 349,97</t>
+          <t>-70,0; 69,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,84; 197,71</t>
+          <t>-62,64; 60,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,29; 77,56</t>
+          <t>-20,9; 384,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,85; 60,68</t>
+          <t>-26,05; 342,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,29; 61,69</t>
+          <t>-61,13; 196,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,55; 108,06</t>
+          <t>-31,72; 107,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 90,99</t>
+          <t>-40,44; 78,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 72,59</t>
+          <t>-46,65; 74,4</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-5,15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-7,25</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,72</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-14,18</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-5,15</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-7,17</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>-3,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 17,92</t>
+          <t>-7,3; 21,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-28,51; -2,13</t>
+          <t>-16,86; 7,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 22,46</t>
+          <t>-18,26; 5,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 21,66</t>
+          <t>-12,92; 17,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 7,55</t>
+          <t>-26,23; 0,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 4,24</t>
+          <t>-15,24; 18,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 14,49</t>
+          <t>-5,63; 13,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 0,34</t>
+          <t>-18,04; -0,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 7,06</t>
+          <t>-13,04; 7,72</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>41,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-29,89%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-42,09%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>8,41%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-69,26%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>41,78%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-29,89%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,6%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-16,71%</t>
+          <t>-18,53%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,73; 143,37</t>
+          <t>-32,98; 192,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-93,05; 8,75</t>
+          <t>-74,46; 76,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,07; 180,06</t>
+          <t>-82,71; 66,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 193,48</t>
+          <t>-46,65; 150,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-76,76; 69,3</t>
+          <t>-92,46; 23,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-80,28; 43,61</t>
+          <t>-56,31; 149,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 106,0</t>
+          <t>-24,61; 94,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,56; 9,83</t>
+          <t>-78,29; 1,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,51; 54,43</t>
+          <t>-59,1; 58,65</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,02</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,69</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,99</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,35</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,93</t>
+          <t>3,46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>5,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 16,04</t>
+          <t>-6,39; 11,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 6,11</t>
+          <t>-8,41; 9,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 11,78</t>
+          <t>-2,05; 16,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 11,35</t>
+          <t>-3,99; 15,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 9,39</t>
+          <t>-10,69; 6,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 18,62</t>
+          <t>-5,44; 12,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 11,21</t>
+          <t>-2,72; 10,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 6,09</t>
+          <t>-6,84; 5,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 12,36</t>
+          <t>-0,61; 12,28</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>43,32%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>29,41%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-10,52%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13,1%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 109,1</t>
+          <t>-29,69; 83,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 43,05</t>
+          <t>-39,69; 66,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 78,44</t>
+          <t>-10,09; 120,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 81,53</t>
+          <t>-16,06; 110,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,56; 67,2</t>
+          <t>-45,75; 49,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 140,24</t>
+          <t>-24,43; 85,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 75,24</t>
+          <t>-12,98; 68,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 38,07</t>
+          <t>-30,43; 38,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 87,18</t>
+          <t>-3,9; 77,71</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,92</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,16</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-6,09</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-6,1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,44</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-5,79</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,92</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,9</t>
+          <t>-9,94</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-6,22</t>
+          <t>-7,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 5,5</t>
+          <t>-5,42; 16,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 8,75</t>
+          <t>-10,64; 12,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 9,32</t>
+          <t>-16,37; 4,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 17,72</t>
+          <t>-18,4; 6,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 11,09</t>
+          <t>-18,63; 8,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 4,92</t>
+          <t>-22,38; 2,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 9,15</t>
+          <t>-8,2; 9,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 6,99</t>
+          <t>-8,59; 7,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 3,53</t>
+          <t>-15,95; 1,35</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28,81%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-29,62%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-20,51%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-14,92%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-19,46%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28,81%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-28,72%</t>
+          <t>-33,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-25,3%</t>
+          <t>-31,96%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,97; 24,99</t>
+          <t>-22,29; 114,65</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 39,6</t>
+          <t>-41,28; 82,38</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 41,83</t>
+          <t>-66,05; 34,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 121,9</t>
+          <t>-49,06; 29,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 70,17</t>
+          <t>-49,44; 38,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,52; 35,96</t>
+          <t>-61,59; 18,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 46,38</t>
+          <t>-28,76; 43,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 34,67</t>
+          <t>-31,17; 37,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 20,35</t>
+          <t>-54,81; 7,36</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>10,83</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>15,43</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-11,36</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-2,99</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-11,94</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>10,83</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>15,43</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>-12,21</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,64</t>
+          <t>-5,78</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 4,32</t>
+          <t>-0,98; 21,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 13,56</t>
+          <t>2,16; 29,24</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-26,05; 1,68</t>
+          <t>-7,85; 14,52</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,2; 23,62</t>
+          <t>-26,84; 5,6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,88; 30,17</t>
+          <t>-19,53; 13,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 14,18</t>
+          <t>-25,82; 1,91</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 9,01</t>
+          <t>-10,23; 11,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 16,2</t>
+          <t>-4,34; 17,19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 3,41</t>
+          <t>-14,72; 4,88</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>147,36%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>210,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>20,74%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-42,61%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-11,22%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-44,8%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>147,36%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>210,0%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>-45,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-32,16%</t>
+          <t>-32,93%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 31,5</t>
+          <t>-21,91; 904,48</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-56,48; 70,04</t>
+          <t>-1,5; 1031,79</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-75,63; 13,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-26,85; 831,82</t>
+          <t>-79,47; 38,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1207,09</t>
+          <t>-58,64; 78,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-85,57; 531,15</t>
+          <t>-74,12; 16,22</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 72,32</t>
+          <t>-47,5; 94,94</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 124,06</t>
+          <t>-21,72; 143,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-64,81; 30,97</t>
+          <t>-66,87; 47,36</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2,95</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1,53</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1,6</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,39</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,84</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-2,95</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2,95</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-2,59</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 5,56</t>
+          <t>-2,08; 8,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,96</t>
+          <t>-3,23; 6,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 2,08</t>
+          <t>-5,9; 3,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 8,24</t>
+          <t>-4,21; 5,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 6,25</t>
+          <t>-7,59; 2,22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 3,63</t>
+          <t>-8,49; 1,24</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 5,25</t>
+          <t>-1,65; 5,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,82</t>
+          <t>-3,97; 2,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 1,33</t>
+          <t>-5,93; 0,72</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-9,4%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-13,89%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-14,41%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-6,61%</t>
+          <t>-17,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-11,1%</t>
+          <t>-13,84%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 32,52</t>
+          <t>-10,36; 53,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 11,93</t>
+          <t>-16,63; 42,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 11,79</t>
+          <t>-30,38; 22,07</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 56,23</t>
+          <t>-18,88; 32,53</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 42,77</t>
+          <t>-32,85; 13,86</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 24,37</t>
+          <t>-36,32; 7,28</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 31,16</t>
+          <t>-8,1; 31,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 16,72</t>
+          <t>-19,23; 16,13</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 8,36</t>
+          <t>-28,75; 4,5</t>
         </is>
       </c>
     </row>
